--- a/iaomr/backend/scripts/mails.xlsx
+++ b/iaomr/backend/scripts/mails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb928b6723e3372b/Desktop/Back end works 24th iaomr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{E0AEC128-A7A3-4AB5-AFBD-6136A1A4325A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7A46664-0DEE-4560-ACDC-E9CF1F027B39}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{E0AEC128-A7A3-4AB5-AFBD-6136A1A4325A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BC5CC80-67C9-4D8A-A524-80C1A7E33455}"/>
   <bookViews>
-    <workbookView xWindow="10572" yWindow="3804" windowWidth="11652" windowHeight="9876" xr2:uid="{BFAAD3AC-98AE-439B-9464-3141CE1CB60B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BFAAD3AC-98AE-439B-9464-3141CE1CB60B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="10" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>No</t>
   </si>
@@ -44,43 +44,115 @@
     <t>Non- Vegetarian</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Post Graduate</t>
+  </si>
+  <si>
+    <t>1st year</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>bhama1504@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.BHAMAVATHANI.V</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1gKBXlqMCGAjBV3VGeerbnVlI4xQmF97Q</t>
+  </si>
+  <si>
+    <t>Tamilnadu</t>
+  </si>
+  <si>
+    <t>Chengalpattu</t>
+  </si>
+  <si>
+    <t>Karpaga Vinayaga Institute of Dental Sciences</t>
+  </si>
+  <si>
+    <t>GST Road, Chinna Kolambakkam(Post), Madhuranthagam(Tk), Chengalpattu(Dt).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Ry6YlO-bA9XJC1BpKkcRLF8LLkwVuSQ6</t>
+  </si>
+  <si>
+    <t>priyasubramanim2510@gmail.com</t>
+  </si>
+  <si>
+    <t>GOKULAPRIYA S</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1s-9I_nmuT17vGbf16s0Uj8I3uNxNjVMF</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>Senior lecturer / Assistant Professor</t>
+  </si>
+  <si>
     <t>INDIA</t>
   </si>
   <si>
+    <t>TAMILNADU</t>
+  </si>
+  <si>
+    <t>NAMAKKAL</t>
+  </si>
+  <si>
+    <t>JKKN DENTAL COLLEGE &amp; HOSPITAL</t>
+  </si>
+  <si>
+    <t>JKKN EDUCATIONAL INSTITUTION</t>
+  </si>
+  <si>
     <t>CASH</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>praveen.vachepally@gmail.com</t>
-  </si>
-  <si>
-    <t>DR. VACHEPALLY PRAVEEM REDDY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=18MmSQbPDIFaro5QM5u5Bz8RrbxyDEjYs</t>
-  </si>
-  <si>
-    <t>Faculty</t>
-  </si>
-  <si>
-    <t>Senior lecturer / Assistant Professor</t>
-  </si>
-  <si>
-    <t>TELENGANA</t>
-  </si>
-  <si>
-    <t>NALGONDA</t>
-  </si>
-  <si>
-    <t>KAMINENI INSTITUTE OF DENTAL SCIENCES</t>
-  </si>
-  <si>
-    <t>TELNGANA</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1RoTLSpwFnY56s_tmu7MdU8rxBKxZWAVz</t>
+    <t>31.07.2026</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cQLnFWvYAWOCY4FRlsnnhspCASWS8pk6</t>
+  </si>
+  <si>
+    <t>drmeenapriyamds14@gmail.com</t>
+  </si>
+  <si>
+    <t>P.K.MEENA PRIYA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1GEmBO_ugqNxHeiPMEa7foHlijPjD2bWx</t>
+  </si>
+  <si>
+    <t>98652 48844</t>
+  </si>
+  <si>
+    <t>Head of the Department</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>Erode</t>
+  </si>
+  <si>
+    <t>JKKN Dental College</t>
+  </si>
+  <si>
+    <t>NH 544, Kumarapalayam, Namakkal District, 638183</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1w6wUbVWV3u7A_WV5CSGn07zS1Yr6MXDS</t>
+  </si>
+  <si>
+    <t>Vegetarian</t>
   </si>
 </sst>
 </file>
@@ -115,7 +187,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,8 +206,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -166,22 +244,82 @@
         <color rgb="FFFFFF00"/>
       </right>
       <top style="medium">
-        <color rgb="FFCFE2F3"/>
-      </top>
-      <bottom style="medium">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00FFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00FFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00FFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00FFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
         <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
+      </right>
+      <top style="medium">
         <color rgb="FFFFFF00"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFE2F3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00FFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -193,40 +331,100 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
         <color rgb="FF00FFFF"/>
       </right>
       <top style="medium">
-        <color rgb="FFCFE2F3"/>
-      </top>
-      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
         <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF00FFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF00FFFF"/>
-      </top>
-      <bottom style="medium">
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
         <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFE2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -238,8 +436,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="22" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -255,20 +456,68 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -614,83 +863,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D2E273-6BB2-4E8E-B401-1AABE0CAB9EF}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1">
-        <v>46228.475138888891</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:37" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11">
+        <v>46232.861597222225</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="12">
+        <v>4471565100</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="15">
+        <v>42141</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="16">
+        <v>7500</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="4">
-        <v>9945009250</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="6">
-        <v>7670</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="8">
-        <v>46228</v>
-      </c>
-      <c r="T1" s="4">
-        <v>297519860460</v>
-      </c>
-      <c r="U1" s="3" t="s">
+      <c r="S1" s="17">
+        <v>46232</v>
+      </c>
+      <c r="T1" s="15">
+        <v>657645887307</v>
+      </c>
+      <c r="U1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="2" t="s">
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="9"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="18"/>
       <c r="AE1" s="10"/>
       <c r="AF1" s="10"/>
       <c r="AG1" s="10"/>
@@ -699,10 +950,174 @@
       <c r="AJ1" s="10"/>
       <c r="AK1" s="10"/>
     </row>
+    <row r="2" spans="1:37" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>46234.412662037037</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5">
+        <v>9443488229</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="5">
+        <v>22621</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="19">
+        <v>6500</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3">
+        <v>72404305820</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="8"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+    </row>
+    <row r="3" spans="1:37" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20">
+        <v>46234.424745370372</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="24">
+        <v>6500</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="25">
+        <v>46233</v>
+      </c>
+      <c r="T3" s="26">
+        <v>837352648972</v>
+      </c>
+      <c r="U3" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" xr:uid="{DFF89EE3-769F-4A57-A334-287D44B48326}"/>
-    <hyperlink ref="U1" r:id="rId2" xr:uid="{9FCF7DD3-3357-48E7-91D8-C5DA63A8451A}"/>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{D366B0EC-A0A0-408B-B23A-8DACD5C0BBF1}"/>
+    <hyperlink ref="U1" r:id="rId2" xr:uid="{1CAB33E6-D364-43CB-AEBA-B374705DCB7F}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{35987631-E3D1-48AD-B129-75D8C8966554}"/>
+    <hyperlink ref="U2" r:id="rId4" xr:uid="{F205C62A-E7EC-4CA8-AF4D-C14B951A1212}"/>
+    <hyperlink ref="E3" r:id="rId5" xr:uid="{6F6250CE-9D55-40C0-88F7-62074783C6A2}"/>
+    <hyperlink ref="U3" r:id="rId6" xr:uid="{91BFCC87-BB74-4040-9540-A17FA0AE3FE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
